--- a/branches/master/ValueSet-condition-valueset.xlsx
+++ b/branches/master/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T08:18:33+00:00</t>
+    <t>2025-02-17T11:04:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-condition-valueset.xlsx
+++ b/branches/master/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:04:00+00:00</t>
+    <t>2025-02-17T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-condition-valueset.xlsx
+++ b/branches/master/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:10:24+00:00</t>
+    <t>2025-02-17T11:11:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-condition-valueset.xlsx
+++ b/branches/master/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:11:10+00:00</t>
+    <t>2025-02-17T11:12:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-condition-valueset.xlsx
+++ b/branches/master/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:12:19+00:00</t>
+    <t>2025-02-17T11:14:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/ValueSet-condition-valueset.xlsx
+++ b/branches/master/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:14:25+00:00</t>
+    <t>2025-02-26T15:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
